--- a/output/details/2026-05-26/preprocessed_data.xlsx
+++ b/output/details/2026-05-26/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46168</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1160482431871511</v>
+        <v>-0.1216519838255625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.141539786758894</v>
+        <v>-0.1407610065888458</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1413490064877736</v>
+        <v>-0.1404855733943692</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.119800768723218</v>
+        <v>-0.004050281722109399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001697325145445958</v>
+        <v>0.001692987492808717</v>
       </c>
       <c r="G2" t="n">
-        <v>1.964710471137659</v>
+        <v>2.517108787170753</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4330523390786865</v>
+        <v>-0.2653707929481132</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
